--- a/building_inspector_forms/010_green_building_certification_inspection_form--building_inspector_forms.xlsx
+++ b/building_inspector_forms/010_green_building_certification_inspection_form--building_inspector_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'single-family',_'value':_'single-family'}</t>
+          <t>single-family</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Single-Family', 'value': 'single-family'}</t>
+          <t>Single-Family</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'multi-family',_'value':_'multi-family'}</t>
+          <t>multi-family</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Multi-Family', 'value': 'multi-family'}</t>
+          <t>Multi-Family</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'commercial',_'value':_'commercial'}</t>
+          <t>commercial</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Commercial', 'value': 'commercial'}</t>
+          <t>Commercial</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'new_construction',_'value':_'new-construction'}</t>
+          <t>new_construction</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'New Construction', 'value': 'new-construction'}</t>
+          <t>New Construction</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'existing',_'value':_'existing'}</t>
+          <t>existing</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Existing', 'value': 'existing'}</t>
+          <t>Existing</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'in_progress',_'value':_'in-progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'In Progress', 'value': 'in-progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'insulation',_'value':_'insulation'}</t>
+          <t>insulation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Insulation', 'value': 'insulation'}</t>
+          <t>Insulation</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'solar_panels',_'value':_'solar-panels'}</t>
+          <t>solar_panels</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Solar Panels', 'value': 'solar-panels'}</t>
+          <t>Solar Panels</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'rainwater_harvesting_system',_'value':_'rainwater-harvesting-system'}</t>
+          <t>rainwater_harvesting_system</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Rainwater Harvesting System', 'value': 'rainwater-harvesting-system'}</t>
+          <t>Rainwater Harvesting System</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'green_roof',_'value':_'green-roof'}</t>
+          <t>green_roof</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Green Roof', 'value': 'green-roof'}</t>
+          <t>Green Roof</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'green_wall',_'value':_'green-wall'}</t>
+          <t>green_wall</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Green Wall', 'value': 'green-wall'}</t>
+          <t>Green Wall</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'greenhouse',_'value':_'greenhouse'}</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Greenhouse', 'value': 'greenhouse'}</t>
+          <t>Greenhouse</t>
         </is>
       </c>
     </row>
@@ -990,12 +990,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'certified',_'value':_'certified'}</t>
+          <t>certified</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Certified', 'value': 'certified'}</t>
+          <t>Certified</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'provisional',_'value':_'provisional'}</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Provisional', 'value': 'provisional'}</t>
+          <t>Provisional</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'denied',_'value':_'denied'}</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Denied', 'value': 'denied'}</t>
+          <t>Denied</t>
         </is>
       </c>
     </row>
